--- a/ORDER GUIDE - TEMPLATE.xlsx
+++ b/ORDER GUIDE - TEMPLATE.xlsx
@@ -1,19 +1,20 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10913"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="11214"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/davidcuvin/purveyor_project/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{61280416-B763-E347-96C3-EAF080031E2E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{643E1548-C0E4-1A48-8BD6-C3FB4C40EF0A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="300" yWindow="1160" windowWidth="29940" windowHeight="17600" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="300" yWindow="1160" windowWidth="29940" windowHeight="17600" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="order_guide" sheetId="2" r:id="rId1"/>
+    <sheet name="protein_order_guide" sheetId="3" r:id="rId2"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -36,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="16" uniqueCount="8">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="21" uniqueCount="11">
   <si>
     <t>Ingredient</t>
   </si>
@@ -61,6 +62,15 @@
   <si>
     <t>Produce / Specialty</t>
   </si>
+  <si>
+    <t>EVENT NAME: EVENT DATE</t>
+  </si>
+  <si>
+    <t>Status</t>
+  </si>
+  <si>
+    <t>Notes</t>
+  </si>
 </sst>
 </file>
 
@@ -69,7 +79,7 @@
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="dddd\ m/d"/>
   </numFmts>
-  <fonts count="7" x14ac:knownFonts="1">
+  <fonts count="8" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -115,8 +125,16 @@
       <family val="2"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <b/>
+      <sz val="16"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
   </fonts>
-  <fills count="3">
+  <fills count="4">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -129,8 +147,14 @@
         <bgColor rgb="FFD8D8D8"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.39997558519241921"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="7">
+  <borders count="10">
     <border>
       <left/>
       <right/>
@@ -218,11 +242,48 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right/>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="15">
+  <cellXfs count="20">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
@@ -267,6 +328,21 @@
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="3" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="3" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="3" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="3" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="3" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -3106,4 +3182,51 @@
   <pageMargins left="0.75" right="0.25" top="0.75" bottom="0.75" header="0" footer="0"/>
   <pageSetup paperSize="9" scale="37" orientation="portrait"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{48052901-73DF-E642-88A8-BC7B2309B5A6}">
+  <dimension ref="A1:D3"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
+  <cols>
+    <col min="1" max="1" width="29.6640625" customWidth="1"/>
+    <col min="2" max="2" width="43.6640625" customWidth="1"/>
+    <col min="3" max="3" width="28.33203125" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:4" ht="21" x14ac:dyDescent="0.2">
+      <c r="A1" s="15" t="s">
+        <v>8</v>
+      </c>
+      <c r="B1" s="15"/>
+      <c r="C1" s="15"/>
+      <c r="D1" s="15"/>
+    </row>
+    <row r="2" spans="1:4" ht="21" x14ac:dyDescent="0.2">
+      <c r="A2" s="17"/>
+      <c r="B2" s="18"/>
+      <c r="C2" s="18"/>
+      <c r="D2" s="19"/>
+    </row>
+    <row r="3" spans="1:4" ht="21" x14ac:dyDescent="0.2">
+      <c r="A3" s="16" t="s">
+        <v>0</v>
+      </c>
+      <c r="B3" s="16" t="s">
+        <v>9</v>
+      </c>
+      <c r="C3" s="16" t="s">
+        <v>2</v>
+      </c>
+      <c r="D3" s="16" t="s">
+        <v>10</v>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="2">
+    <mergeCell ref="A1:D1"/>
+    <mergeCell ref="A2:D2"/>
+  </mergeCells>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
 </file>